--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/valparaiso.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M306"/>
+  <dimension ref="A1:M308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1423.94</v>
+        <v>1411.88</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7253.71</v>
+        <v>7192.27</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>23523.45</v>
+        <v>23324.22</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>515.9</v>
+        <v>511.53</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>39311.56</v>
+        <v>38978.62</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3906.08</v>
+        <v>3886.01</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1817.12</v>
+        <v>1807.78</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5472.39</v>
+        <v>5444.27</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2670.1</v>
+        <v>2643.45</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>203.06</v>
+        <v>200.93</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8228.73</v>
+        <v>8183.75</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4768.21</v>
+        <v>4742.15</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5087.97</v>
+        <v>5060.16</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>21320.99</v>
+        <v>21083.45</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>640.34</v>
+        <v>633.21</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>50061.16</v>
+        <v>49503.41</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>527.95</v>
+        <v>522.0700000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>18122.84</v>
+        <v>18023.6</v>
       </c>
     </row>
     <row r="20">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>60917.12</v>
+        <v>60583.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4301-692-CM25</t>
+          <t>945256-89-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>61.980.790-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>Zona de Bienestar Valparaíso</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>28188.6</v>
+        <v>1062.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>945256-89-CM25</t>
+          <t>4301-692-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.980.790-1</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valparaíso</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1068.72</v>
+        <v>28034.22</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>69039.41</v>
+        <v>68951.53</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2821.42</v>
+        <v>2817.83</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>25008.08</v>
+        <v>25280.08</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1731.86</v>
+        <v>1761.76</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2910.18</v>
+        <v>2960.42</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>15069.02</v>
+        <v>15329.14</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3740.52</v>
+        <v>3766.44</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>32061.64</v>
+        <v>32210.96</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>20002.61</v>
+        <v>20146.82</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>17145.61</v>
+        <v>17074.94</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>21320.99</v>
+        <v>21233.12</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3309.83</v>
+        <v>3296.19</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>15229.28</v>
+        <v>15166.51</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>22272.32</v>
+        <v>22237.8</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>152.29</v>
+        <v>153.08</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1707559.25</v>
+        <v>1716377.79</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1295.5</v>
+        <v>1302.19</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6589.2</v>
+        <v>6623.23</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>21384.96</v>
+        <v>21535.88</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>545.75</v>
+        <v>538.7</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>12189.1</v>
+        <v>12031.55</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16718.55</v>
+        <v>16506.19</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>37111.31</v>
+        <v>36639.92</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1267.9</v>
+        <v>1255.28</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2420.53</v>
+        <v>2396.45</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>115.26</v>
+        <v>114.12</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>192.11</v>
+        <v>190.19</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>26109.44</v>
+        <v>25849.66</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1294.41</v>
+        <v>1281.54</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3831.42</v>
+        <v>3793.3</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1391.8</v>
+        <v>1377.96</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>5457.54</v>
+        <v>5437.97</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>605.13</v>
+        <v>602.96</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>60660.6</v>
+        <v>60529.33</v>
       </c>
     </row>
     <row r="57">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>44052.04</v>
+        <v>43867.36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057379-1985-CM25</t>
+          <t>2200-437-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.606.703-6</t>
+          <t>61.606.700-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
+          <t>SERVICIO DE SALUD ACONCAGUA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3336.33</v>
+        <v>711451.9300000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2200-437-CM25</t>
+          <t>1057379-1985-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.606.700-1</t>
+          <t>61.606.703-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>714447.1</v>
+        <v>3322.35</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>9799.57</v>
+        <v>9686.16</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>25110.9</v>
+        <v>24820.29</v>
       </c>
     </row>
     <row r="62">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>15390.33</v>
+        <v>15259.96</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1943-742-CM25</t>
+          <t>3680-539-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>890.67</v>
+        <v>21474.53</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3680-539-CM25</t>
+          <t>1943-740-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>21491.81</v>
+        <v>627.11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1943-740-CM25</t>
+          <t>629373-423-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.962.500-4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>627.62</v>
+        <v>24997.27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>629373-423-CM25</t>
+          <t>629373-424-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>25017.38</v>
+        <v>24997.27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>629373-424-CM25</t>
+          <t>1943-742-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4499,17 +4499,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>70.962.500-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>25017.38</v>
+        <v>889.95</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>240.13</v>
+        <v>241.22</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>7492.12</v>
+        <v>7511.98</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7060.48</v>
+        <v>7050.58</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1397.27</v>
+        <v>1395.31</v>
       </c>
     </row>
     <row r="72">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3929.43</v>
+        <v>3923.92</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4686-844-CM25</t>
+          <t>1057374-698-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.202.000-2</t>
+          <t>61.602.042-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cámara de Diputados de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>59106.42</v>
+        <v>14910.57</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057374-698-CM25</t>
+          <t>4686-844-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4926,17 +4926,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.042-0</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>14808.64</v>
+        <v>59513.26</v>
       </c>
     </row>
     <row r="75">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2183.02</v>
+        <v>2206.43</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1111432-742-CM25</t>
+          <t>1108338-307-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.287.560-5</t>
+          <t>69.287.570-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano San Felipe</t>
+          <t>CONSULTORIO GENERAL N°2 DE LOS ANDES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>18756.93</v>
+        <v>12211.98</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1108338-307-CM25</t>
+          <t>1111432-742-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.287.570-2</t>
+          <t>69.287.560-5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL N°2 DE LOS ANDES</t>
+          <t>Consultorio General Urbano San Felipe</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>12063.72</v>
+        <v>18987.46</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>36019.79</v>
+        <v>36462.48</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>17969.02</v>
+        <v>18199.91</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>23027.7</v>
+        <v>23323.6</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3629.27</v>
+        <v>3675.9</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>362.93</v>
+        <v>367.59</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4633.54</v>
+        <v>4693.08</v>
       </c>
     </row>
     <row r="84">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>13622.03</v>
+        <v>13797.07</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1057379-2023-CM25</t>
+          <t>1702-995-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.606.703-6</t>
+          <t>61.606.605-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>18088.37</v>
+        <v>36216.77</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>898-7412-CM25</t>
+          <t>1057379-2023-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.606.703-6</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>21775.6</v>
+        <v>18187.29</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1702-995-CM25</t>
+          <t>898-7412-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.605-6</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>36019.79</v>
+        <v>21894.69</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>69993</v>
+        <v>70375.78</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3074.47</v>
+        <v>2995.96</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3970.97</v>
+        <v>3869.57</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>16625.65</v>
+        <v>16387.35</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>7890.58</v>
+        <v>7776.87</v>
       </c>
     </row>
     <row r="93">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>72542.41</v>
+        <v>71604.84</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>619133-251-CM26</t>
+          <t>4280-5-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6146,17 +6146,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>69.050.900-8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>I MUNICIPALIDAD DE CATEMU</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>10164.75</v>
+        <v>2384.62</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4280-5-CM26</t>
+          <t>619133-251-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.050.900-8</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CATEMU</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2384.6</v>
+        <v>10164.81</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>838794-9-CM26</t>
+          <t>838794-10-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>9371.4</v>
+        <v>3570.41</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>838794-10-CM26</t>
+          <t>838794-9-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3572.85</v>
+        <v>9365</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>6577.63</v>
+        <v>6542.88</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>22568.75</v>
+        <v>22427.32</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>56563.28</v>
+        <v>56933.99</v>
       </c>
     </row>
     <row r="101">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>18173.22</v>
+        <v>18449.89</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2170-62-CM26</t>
+          <t>1057374-56-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.602.042-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>8939.91</v>
+        <v>13141.88</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>24420.15</v>
+        <v>25013.99</v>
       </c>
     </row>
     <row r="104">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>22729.95</v>
+        <v>23282.69</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1057374-56-CM26</t>
+          <t>2170-62-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.602.042-0</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>12829.88</v>
+        <v>9157.309999999999</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3047-24-CM26</t>
+          <t>3117-171-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6878,17 +6878,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>61.102.006-6</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2262.25</v>
+        <v>23924.94</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3117-171-CM26</t>
+          <t>3047-24-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6939,17 +6939,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.102.006-6</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>Academia Politécnica Naval</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>23220.81</v>
+        <v>2330.85</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1099899-10-CM26</t>
+          <t>813685-8-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>7461.23</v>
+        <v>75876.13</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4968-156-CM26</t>
+          <t>4968-155-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4134.67</v>
+        <v>1586.87</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1099899-11-CM26</t>
+          <t>4968-156-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1488.57</v>
+        <v>4257.56</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>813685-8-CM26</t>
+          <t>1099899-10-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARIT Y MM (AB)</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>73685.97</v>
+        <v>7683</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4968-155-CM26</t>
+          <t>1099899-11-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1541.07</v>
+        <v>1532.82</v>
       </c>
     </row>
     <row r="113">
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>22625.31</v>
+        <v>23297.81</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3160-8-CM26</t>
+          <t>3111-1-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.102.003-1</t>
+          <t>61.966.600-3</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE LOS SERVICIOS DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE FINANZAS DE LA ARMADA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2412.12</v>
+        <v>62050.17</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3111-1-CM26</t>
+          <t>3160-8-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.966.600-3</t>
+          <t>61.102.003-1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE FINANZAS DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE LOS SERVICIOS DE LA ARMADA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>61870.94</v>
+        <v>2419.11</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2320.13</v>
+        <v>2326.5</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>23143.31</v>
+        <v>23353.82</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>17043.66</v>
+        <v>17198.69</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5512.43</v>
+        <v>5548.74</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>9595.540000000001</v>
+        <v>9658.74</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>29973.9</v>
+        <v>30171.3</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1740.1</v>
+        <v>1751.56</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3747.13</v>
+        <v>3743.27</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>191412.19</v>
+        <v>190040.92</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>7685.68</v>
+        <v>7640.39</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>11728.47</v>
+        <v>11657.21</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>18360.36</v>
+        <v>18248.8</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>23201.32</v>
+        <v>23111.77</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>15539.08</v>
+        <v>15479.11</v>
       </c>
     </row>
     <row r="130">
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>6146.03</v>
+        <v>6177.85</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2170-183-CM26</t>
+          <t>617807-1211-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3857.22</v>
+        <v>19886.44</v>
       </c>
     </row>
     <row r="132">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1482.49</v>
+        <v>1483.92</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>617807-1211-CM26</t>
+          <t>2170-185-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>19867.29</v>
+        <v>4929.31</v>
       </c>
     </row>
     <row r="134">
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>7337.09</v>
+        <v>7344.16</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2170-182-CM26</t>
+          <t>2170-183-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>25639.49</v>
+        <v>3860.94</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2170-184-CM26</t>
+          <t>2170-182-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>385.72</v>
+        <v>25664.2</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2170-185-CM26</t>
+          <t>2170-184-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>4924.57</v>
+        <v>386.09</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>12424.54</v>
+        <v>12455.1</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2198.06</v>
+        <v>2169.76</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>13955.92</v>
+        <v>13776.25</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>21925.65</v>
+        <v>21770.92</v>
       </c>
     </row>
     <row r="142">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>24822.66</v>
+        <v>25272.71</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3544-41-CM26</t>
+          <t>2512-6-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2198.06</v>
+        <v>401.85</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2512-5-CM26</t>
+          <t>3544-41-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>351.69</v>
+        <v>2232.49</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2512-6-CM26</t>
+          <t>4968-389-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>395.65</v>
+        <v>170.36</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4968-388-CM26</t>
+          <t>2512-5-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>3857.82</v>
+        <v>357.2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>4968-389-CM26</t>
+          <t>4968-388-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>167.73</v>
+        <v>3918.25</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>207795.82</v>
+        <v>207785.13</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2039.43</v>
+        <v>2030.31</v>
       </c>
     </row>
     <row r="150">
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3604.85</v>
+        <v>3607.95</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1953-418-CM26</t>
+          <t>2755-62-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9627,17 +9627,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>5495.15</v>
+        <v>544.49</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2755-62-CM26</t>
+          <t>1953-418-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9688,17 +9688,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>544.02</v>
+        <v>5499.88</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>8861.290000000001</v>
+        <v>8897.9</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1098.18</v>
+        <v>1095.15</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1373.79</v>
+        <v>1357.93</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>55866.78</v>
+        <v>55033.51</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>15752.68</v>
+        <v>15662.19</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2527.77</v>
+        <v>2511.58</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>6261.97</v>
+        <v>6221.85</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>4396.12</v>
+        <v>4367.96</v>
       </c>
     </row>
     <row r="161">
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>15452.89</v>
+        <v>15386.32</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1702-197-CM26</t>
+          <t>1705-218-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>61.606.605-6</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>32970.9</v>
+        <v>22745.92</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1705-218-CM26</t>
+          <t>1702-197-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>61.606.605-6</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10394,13 +10394,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>23079.82</v>
+        <v>32493.91</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2170-313-CM26</t>
+          <t>1099402-153-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10425,12 +10425,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>62.000.620-3</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10455,13 +10455,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>15877.83</v>
+        <v>12259.38</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2170-314-CM26</t>
+          <t>2170-316-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3654.27</v>
+        <v>4565.09</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2170-315-CM26</t>
+          <t>2170-314-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>365.43</v>
+        <v>3575.65</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2170-316-CM26</t>
+          <t>2170-313-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>4665.47</v>
+        <v>15536.21</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1099402-153-CM26</t>
+          <t>2170-315-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>62.000.620-3</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>12528.94</v>
+        <v>357.57</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>28685.01</v>
+        <v>28017.54</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>5534.66</v>
+        <v>5405.87</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>11137.27</v>
+        <v>10782.14</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1114.28</v>
+        <v>1078.74</v>
       </c>
     </row>
     <row r="173">
@@ -11004,13 +11004,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4777.89</v>
+        <v>4652.07</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1057370-209-CM26</t>
+          <t>898-1182-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11065,13 +11065,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>12590.68</v>
+        <v>21815.92</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>898-1182-CM26</t>
+          <t>1057370-209-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>22218.85</v>
+        <v>12362.35</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>470.44</v>
+        <v>471.81</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>37885.36</v>
+        <v>38042.82</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>946.67</v>
+        <v>954.7</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4025.24</v>
+        <v>4059.4</v>
       </c>
     </row>
     <row r="180">
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2723.36</v>
+        <v>2746.48</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1173933-13-CM26</t>
+          <t>3446-73-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>60.905.015-2</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11492,13 +11492,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5494.42</v>
+        <v>1127.43</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>707419-33-CM26</t>
+          <t>1173933-13-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11518,17 +11518,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.905.015-2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11553,13 +11553,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>4851.39</v>
+        <v>5562.04</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3446-73-CM26</t>
+          <t>707419-33-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11579,17 +11579,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11614,13 +11614,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1113.73</v>
+        <v>4911.1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1953-653-CM26</t>
+          <t>3446-91-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11645,12 +11645,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>303.54</v>
+        <v>1128.55</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>619133-2112-CM26</t>
+          <t>4469-189-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11701,17 +11701,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11736,13 +11736,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>28844.62</v>
+        <v>268.03</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>4469-189-CM26</t>
+          <t>1953-653-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11762,17 +11762,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11797,13 +11797,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>264.51</v>
+        <v>307.58</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>3446-91-CM26</t>
+          <t>619133-2112-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1113.73</v>
+        <v>29228.62</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1113.73</v>
+        <v>1134.79</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>31741.22</v>
+        <v>32341.53</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>588.05</v>
+        <v>591.8099999999999</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>24502.48</v>
+        <v>24579.57</v>
       </c>
     </row>
     <row r="192">
@@ -12163,13 +12163,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>22663.23</v>
+        <v>22734.53</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2170-411-CM26</t>
+          <t>2170-412-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12224,13 +12224,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>21258.68</v>
+        <v>8829</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2170-412-CM26</t>
+          <t>2170-411-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>8801.309999999999</v>
+        <v>21325.57</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>166.96</v>
+        <v>167.3</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2227.18</v>
+        <v>2231.79</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>8909.82</v>
+        <v>8928.27</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>13331.31</v>
+        <v>13358.93</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1670.59</v>
+        <v>1674.05</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>4496.67</v>
+        <v>4505.99</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>529.02</v>
+        <v>530.12</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>38918.63</v>
+        <v>38751.44</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1670.59</v>
+        <v>1663.41</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>18644.79</v>
+        <v>18564.7</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>719.67</v>
+        <v>715.35</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>4026.35</v>
+        <v>3992.01</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2453.34</v>
+        <v>2432.42</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>13853.58</v>
+        <v>13735.42</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>15663.87</v>
+        <v>15748.22</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1671.05</v>
+        <v>1680.05</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>9656.09</v>
+        <v>9729.23</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>22225</v>
+        <v>22393.34</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2676.22</v>
+        <v>2686.36</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>26898.92</v>
+        <v>27000.82</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>3810</v>
+        <v>3800.38</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1113.94</v>
+        <v>1111.13</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1559.65</v>
+        <v>1571.27</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>557.02</v>
+        <v>550.96</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>4026.35</v>
+        <v>3982.56</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3200.18</v>
+        <v>3165.37</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>464.5</v>
+        <v>459.45</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>33421.05</v>
+        <v>33345.19</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>623.41</v>
+        <v>621.87</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2005.26</v>
+        <v>2015.11</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>50864.55</v>
+        <v>51114.41</v>
       </c>
     </row>
     <row r="226">
@@ -14237,13 +14237,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>382.65</v>
+        <v>383.92</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1099402-248-CM26</t>
+          <t>1079516-522-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14268,12 +14268,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>62.000.620-3</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+          <t>SECCIÓN COMPRAS V ZONA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>13758.33</v>
+        <v>70244.17</v>
       </c>
     </row>
     <row r="228">
@@ -14359,13 +14359,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>71164.44</v>
+        <v>71400.52</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1079516-522-CM26</t>
+          <t>1099402-248-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14390,12 +14390,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>62.000.620-3</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14420,13 +14420,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>70011.92</v>
+        <v>13803.97</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1079516-520-CM26</t>
+          <t>1705-354-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14451,12 +14451,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14481,13 +14481,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>45352.75</v>
+        <v>23472.53</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1705-354-CM26</t>
+          <t>1111432-326-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>69.287.560-5</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>Consultorio General Urbano San Felipe</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14542,13 +14542,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>23394.92</v>
+        <v>38021.56</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1111432-326-CM26</t>
+          <t>1079516-520-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>69.287.560-5</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano San Felipe</t>
+          <t>SECCIÓN COMPRAS V ZONA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>37895.84</v>
+        <v>45503.2</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>4533.9</v>
+        <v>4548.33</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>23502.94</v>
+        <v>23577.74</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>10476.46</v>
+        <v>10509.8</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>16048.46</v>
+        <v>16133.8</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>630.96</v>
+        <v>639.99</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>15564.23</v>
+        <v>15786.94</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>36278.16</v>
+        <v>36703.72</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>77486.41</v>
+        <v>78395.37</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2479.45</v>
+        <v>2521.39</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>625.7</v>
+        <v>636.28</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>15016.86</v>
+        <v>15169.58</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>22083.63</v>
+        <v>21916.09</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2258.16</v>
+        <v>2220.01</v>
       </c>
     </row>
     <row r="246">
@@ -15457,13 +15457,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>14391.16</v>
+        <v>14193.42</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>619133-3106-CM26</t>
+          <t>2755-209-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15488,12 +15488,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -15518,13 +15518,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>27992.57</v>
+        <v>25896.02</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2755-209-CM26</t>
+          <t>619133-3106-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15549,12 +15549,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>26057.57</v>
+        <v>27819.02</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>26057.57</v>
+        <v>25896.02</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>74347.14999999999</v>
+        <v>74684.81</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>81649.47</v>
+        <v>82020.28999999999</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>21917.58</v>
+        <v>22243.94</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>77486.39999999999</v>
+        <v>78640.2</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1660.42</v>
+        <v>1685.15</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>32316.66</v>
+        <v>32931.05</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1051.6</v>
+        <v>1075.32</v>
       </c>
     </row>
     <row r="257">
@@ -16128,13 +16128,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1156.76</v>
+        <v>1182.85</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1099402-301-CM26</t>
+          <t>2170-646-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16159,12 +16159,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>62.000.620-3</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16189,13 +16189,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>16272.15</v>
+        <v>9000.120000000001</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>900-646-CM26</t>
+          <t>2170-645-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16220,12 +16220,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.979.910-0</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16250,13 +16250,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1817.83</v>
+        <v>21863.31</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2170-645-CM26</t>
+          <t>1099402-301-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16281,12 +16281,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>62.000.620-3</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16311,13 +16311,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>21921.29</v>
+        <v>16229.11</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2170-646-CM26</t>
+          <t>900-646-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16342,12 +16342,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.979.910-0</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16372,13 +16372,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>9023.99</v>
+        <v>1813.02</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>3111-21-CM26</t>
+          <t>1705-425-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16403,12 +16403,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.966.600-3</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE FINANZAS DE LA ARMADA</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>11715.95</v>
+        <v>23876.4</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>4127.08</v>
+        <v>4046.3</v>
       </c>
     </row>
     <row r="264">
@@ -16555,13 +16555,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>6845.12</v>
+        <v>6711.14</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1705-425-CM26</t>
+          <t>3111-21-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16586,12 +16586,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>61.966.600-3</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>DIRECCION GENERAL DE FINANZAS DE LA ARMADA</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16616,13 +16616,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>24353.08</v>
+        <v>11486.62</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1099834-79-CM26</t>
+          <t>617807-3650-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16642,17 +16642,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>62.000.640-8</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16677,13 +16677,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>5534.74</v>
+        <v>20453.6</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>617807-3650-CM26</t>
+          <t>898-2154-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16738,13 +16738,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>20761.2</v>
+        <v>20720.42</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>898-2154-CM26</t>
+          <t>1099834-79-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16769,12 +16769,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>62.000.640-8</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>21032.02</v>
+        <v>5452.74</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>33208.46</v>
+        <v>32525.97</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>3364.63</v>
+        <v>3377.76</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>626.34</v>
+        <v>629.53</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>15579.98</v>
+        <v>15640.63</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>12526.72</v>
+        <v>12575.48</v>
       </c>
     </row>
     <row r="274">
@@ -17165,13 +17165,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3451.24</v>
+        <v>3464.68</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1422825-1215-CM26</t>
+          <t>3544-156-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17196,12 +17196,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>75190.39</v>
+        <v>1068.71</v>
       </c>
     </row>
     <row r="276">
@@ -17287,13 +17287,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5262.17</v>
+        <v>5235.51</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>3544-156-CM26</t>
+          <t>1422825-1215-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17318,12 +17318,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17348,13 +17348,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1074.15</v>
+        <v>74809.5</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>377-299-CM26</t>
+          <t>894-27-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17374,17 +17374,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>25905.19</v>
+        <v>2681.3</v>
       </c>
     </row>
     <row r="279">
@@ -17470,13 +17470,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>8116.08</v>
+        <v>8133.38</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>894-27-CM26</t>
+          <t>377-299-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17496,17 +17496,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>2675.6</v>
+        <v>25960.4</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>966.73</v>
+        <v>973.04</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>28560.92</v>
+        <v>28626.42</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1073.54</v>
+        <v>1080.73</v>
       </c>
     </row>
     <row r="284">
@@ -17775,13 +17775,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>3742.33</v>
+        <v>3768.52</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1943-234-CM26</t>
+          <t>742475-60-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17801,17 +17801,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17821,12 +17821,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>513.14</v>
+        <v>10774.53</v>
       </c>
     </row>
     <row r="286">
@@ -17897,13 +17897,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>193.35</v>
+        <v>192.74</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>742475-60-CM26</t>
+          <t>1943-234-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17923,17 +17923,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -17943,12 +17943,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K287" t="inlineStr"/>
@@ -17958,13 +17958,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>10808.67</v>
+        <v>511.52</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2170-711-CM26</t>
+          <t>4968-1071-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17989,12 +17989,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18019,13 +18019,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>23377.07</v>
+        <v>6685.34</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2170-712-CM26</t>
+          <t>4968-1070-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18050,12 +18050,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18080,13 +18080,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>8756.6</v>
+        <v>3996.08</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>4968-1070-CM26</t>
+          <t>2170-712-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18111,12 +18111,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18141,13 +18141,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>4004.79</v>
+        <v>8737.549999999999</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>4968-1071-CM26</t>
+          <t>2170-711-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18172,12 +18172,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>6699.92</v>
+        <v>23326.21</v>
       </c>
     </row>
     <row r="292">
@@ -18263,13 +18263,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>2156.89</v>
+        <v>2144.41</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>945256-48-CM26</t>
+          <t>838794-171-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18294,12 +18294,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.980.790-1</t>
+          <t>61.980.420-1</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valparaíso</t>
+          <t>CENTRAL DE ATENCION PRIMARIA DE SALUD DE LA ARMADA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18324,13 +18324,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1611.22</v>
+        <v>9596.57</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>3515-345-CM26</t>
+          <t>1705-487-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18350,17 +18350,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18385,13 +18385,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1074.15</v>
+        <v>24309.3</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>838794-171-CM26</t>
+          <t>3515-345-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18411,17 +18411,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.980.420-1</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>CENTRAL DE ATENCION PRIMARIA DE SALUD DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18446,13 +18446,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>9752.950000000001</v>
+        <v>1056.93</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1705-487-CM26</t>
+          <t>945256-48-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18477,12 +18477,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>61.980.790-1</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>Zona de Bienestar Valparaíso</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18507,13 +18507,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>24705.42</v>
+        <v>1585.39</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3544-176-CM26</t>
+          <t>2186-649-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18538,12 +18538,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.606.607-2</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18568,13 +18568,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1611.22</v>
+        <v>12257.15</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1099402-360-CM26</t>
+          <t>377-322-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18594,17 +18594,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>62.000.620-3</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18629,13 +18629,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>14737.32</v>
+        <v>23561.59</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>377-322-CM26</t>
+          <t>3544-176-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18655,17 +18655,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18690,13 +18690,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>23838.97</v>
+        <v>1592.48</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2186-649-CM26</t>
+          <t>1099402-360-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.606.607-2</t>
+          <t>62.000.620-3</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>12401.45</v>
+        <v>14565.84</v>
       </c>
     </row>
     <row r="301">
@@ -18812,13 +18812,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>32224.45</v>
+        <v>32045.8</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1099834-88-CM26</t>
+          <t>898-2419-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18843,12 +18843,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>62.000.640-8</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18873,13 +18873,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>12889.78</v>
+        <v>20308.48</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>898-2419-CM26</t>
+          <t>1099834-88-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18904,12 +18904,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>62.000.640-8</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>20408.82</v>
+        <v>12826.41</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>7304.21</v>
+        <v>7268.3</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>1476.05</v>
+        <v>1485.93</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,129 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>7908.25</v>
+        <v>7961.19</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>3624-426-CM26</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>69.060.600-3</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="n">
+        <v>37019.28</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>619133-4443-CM26</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>61.602.038-2</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="n">
+        <v>212.45</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/valparaiso.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/valparaiso.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +21037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +21102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +21167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +22012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +22077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +22142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +22207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +23052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +23117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +23182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +23247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +24027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +24092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +24157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +24222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +24287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +24352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +25002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +25067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +25132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +25197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +25262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +25327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +26042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +26107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +26172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +26237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +26302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +26367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +27017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +27082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +27147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +27212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +27277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +27342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +28057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +28122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +28187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +28252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +28317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +28382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +29032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +29097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +29162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +29227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +29292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +29357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +30007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +30072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +30137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +30202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +30267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +30332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +30397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +30462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +31047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +31112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +31177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +31242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +31307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +31372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +31437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +31697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +32022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +32087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +32152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +32217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +32282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +32347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +32412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +32477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +33062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +33127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +33192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +33257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +33322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +33387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +33452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +33517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +33582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +34037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +34102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +34167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +34232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +34297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +34362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +34427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +34492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +34687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32774,7 +34882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32835,7 +34947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32896,7 +35012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +35077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33018,7 +35142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33079,7 +35207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33140,7 +35272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +35337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +35402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33323,7 +35467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33384,7 +35532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +35597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33506,7 +35662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33567,7 +35727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33628,7 +35792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33689,7 +35857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33872,7 +36052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33933,7 +36117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33994,7 +36182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34055,7 +36247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +36312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34177,7 +36377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +36442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34299,7 +36507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34360,7 +36572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +36637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34482,7 +36702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34726,7 +36962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +37027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +37092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34909,7 +37157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34970,7 +37222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +37287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35092,7 +37352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35153,7 +37417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35214,7 +37482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +37547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35336,7 +37612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +37677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +37807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35702,7 +38002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35763,7 +38067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +38132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35885,7 +38197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35946,7 +38262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36007,7 +38327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36068,7 +38392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +38457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36190,7 +38522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36251,7 +38587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +38652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +38717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36495,7 +38847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36556,7 +38912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36617,7 +38977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36678,7 +39042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +39107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +39172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +39237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36922,7 +39302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +39367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37044,7 +39432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +39497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37166,7 +39562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +39627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37288,7 +39692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37349,7 +39757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +39822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37471,7 +39887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +39952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +40017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +40082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +40147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +40212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37837,7 +40277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37898,7 +40342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +40407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +40472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38081,7 +40537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +40602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38203,7 +40667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +40732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +40797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38447,7 +40927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38569,7 +41057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +41122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +41187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +41252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38813,7 +41317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38874,7 +41382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +41447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +41512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +41577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39118,7 +41642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39179,7 +41707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39240,7 +41772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39301,7 +41837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +41902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +41967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39484,7 +42032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +42097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39606,7 +42162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +42227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39728,7 +42292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +42357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39850,7 +42422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39911,7 +42487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39972,7 +42552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40033,7 +42617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40094,7 +42682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40155,7 +42747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40216,7 +42812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40277,7 +42877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40338,7 +42942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40399,7 +43007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40460,7 +43072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40521,7 +43137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40582,7 +43202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40643,7 +43267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40704,7 +43332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40765,7 +43397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40826,7 +43462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40887,7 +43527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40948,7 +43592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41009,7 +43657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41070,7 +43722,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41131,7 +43787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41192,7 +43852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41253,7 +43917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41314,7 +43982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41375,7 +44047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41436,7 +44112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41497,7 +44177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41558,7 +44242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41619,7 +44307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41680,7 +44372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41741,7 +44437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41802,7 +44502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41863,7 +44567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41924,7 +44632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41985,7 +44697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42046,7 +44762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42107,7 +44827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42168,7 +44892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42229,7 +44957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42290,7 +45022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42351,7 +45087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42412,7 +45152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42473,7 +45217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42534,7 +45282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42595,7 +45347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42656,7 +45412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42717,7 +45477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42778,7 +45542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42839,7 +45607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42900,7 +45672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42961,7 +45737,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43022,7 +45802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43083,7 +45867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43144,7 +45932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43205,7 +45997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43266,7 +46062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43327,7 +46127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43388,7 +46192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43449,7 +46257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43510,7 +46322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43636,7 +46452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43697,7 +46517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43758,7 +46582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43819,7 +46647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43880,7 +46712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43941,7 +46777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44002,7 +46842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44063,7 +46907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44124,7 +46972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44185,7 +47037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44246,7 +47102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44307,7 +47167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44368,7 +47232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44429,7 +47297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44490,7 +47362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44551,7 +47427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44612,7 +47492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44673,7 +47557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44734,7 +47622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44795,7 +47687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44856,7 +47752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44917,7 +47817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44978,7 +47882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45039,7 +47947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45100,7 +48012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45161,7 +48077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45222,7 +48142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45283,7 +48207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45344,7 +48272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45405,7 +48337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45466,7 +48402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45527,7 +48467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45588,7 +48532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45649,7 +48597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45710,7 +48662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45771,7 +48727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45832,7 +48792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45893,7 +48857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45954,7 +48922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46015,7 +48987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46076,7 +49052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46137,7 +49117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46198,7 +49182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46259,7 +49247,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L751" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46320,7 +49312,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46381,7 +49377,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46442,7 +49442,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46503,7 +49507,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46564,7 +49572,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46625,7 +49637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46686,7 +49702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46747,7 +49767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46808,7 +49832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46869,7 +49897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46930,7 +49962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46991,7 +50027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/valparaiso.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M782"/>
+  <dimension ref="A1:M787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1099,7 +1099,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057370-46-CM25</t>
+          <t>619133-321-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>14628.19</v>
+        <v>21364.53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>619133-321-CM25</t>
+          <t>1057370-46-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>21364.53</v>
+        <v>14628.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3530-3-CM25</t>
+          <t>3530-2-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>988.8</v>
+        <v>2473.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3530-2-CM25</t>
+          <t>3530-3-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2473.12</v>
+        <v>988.8</v>
       </c>
     </row>
     <row r="15">
@@ -1749,7 +1749,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3111-3-CM25</t>
+          <t>4968-135-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.966.600-3</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>53881.96</v>
+        <v>3540.56</v>
       </c>
     </row>
     <row r="22">
@@ -1879,7 +1879,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4968-135-CM25</t>
+          <t>3111-3-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.966.600-3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3540.56</v>
+        <v>53881.96</v>
       </c>
     </row>
     <row r="24">
@@ -2204,7 +2204,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3536-13-CM25</t>
+          <t>1057379-1443-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.101.025-7</t>
+          <t>61.606.703-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6137.61</v>
+        <v>1939.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3536-14-CM25</t>
+          <t>1108338-19-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.101.025-7</t>
+          <t>69.287.570-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CONSULTORIO GENERAL N°2 DE LOS ANDES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2045.87</v>
+        <v>12275.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1108338-19-CM25</t>
+          <t>4686-71-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.287.570-2</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL N°2 DE LOS ANDES</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>12275.47</v>
+        <v>19435.75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057379-1443-CM25</t>
+          <t>3536-13-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.606.703-6</t>
+          <t>61.101.025-7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1939.69</v>
+        <v>6137.61</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4686-71-CM25</t>
+          <t>3536-14-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2484,17 +2484,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.202.000-2</t>
+          <t>61.101.025-7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cámara de Diputados de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>19435.75</v>
+        <v>2045.87</v>
       </c>
     </row>
     <row r="33">
@@ -2919,7 +2919,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>617807-1529-CM25</t>
+          <t>707419-14-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>15517.23</v>
+        <v>70621.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>813685-26-CM25</t>
+          <t>617807-1529-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3004,17 +3004,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>19629.78</v>
+        <v>15517.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>707419-14-CM25</t>
+          <t>813685-26-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>70621.19</v>
+        <v>19629.78</v>
       </c>
     </row>
     <row r="42">
@@ -3179,7 +3179,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>945256-19-CM25</t>
+          <t>4848-72-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3199,17 +3199,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.980.790-1</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,13 +3238,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2121.94</v>
+        <v>16925.73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4848-72-CM25</t>
+          <t>945256-19-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3264,17 +3264,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>61.980.790-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16925.73</v>
+        <v>2121.94</v>
       </c>
     </row>
     <row r="45">
@@ -4089,7 +4089,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2186-246-CM25</t>
+          <t>813685-45-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.606.607-2</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6062.57</v>
+        <v>2316.58</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>813685-45-CM25</t>
+          <t>1173463-30-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.969.000-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2316.58</v>
+        <v>485.01</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1173463-30-CM25</t>
+          <t>2186-246-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.969.000-1</t>
+          <t>61.606.607-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>485.01</v>
+        <v>6062.57</v>
       </c>
     </row>
     <row r="60">
@@ -4804,7 +4804,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1108338-67-CM25</t>
+          <t>813685-47-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.287.570-2</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL N°2 DE LOS ANDES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>17823.93</v>
+        <v>46712.21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3536-41-CM25</t>
+          <t>3536-40-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2145.6</v>
+        <v>6436.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3536-40-CM25</t>
+          <t>3536-41-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6436.8</v>
+        <v>2145.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>813685-47-CM25</t>
+          <t>1108338-67-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>69.287.570-2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CONSULTORIO GENERAL N°2 DE LOS ANDES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>46712.21</v>
+        <v>17823.93</v>
       </c>
     </row>
     <row r="72">
@@ -5194,7 +5194,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2221-19-CM25</t>
+          <t>3132-138-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.511.055-k</t>
+          <t>61.950.800-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE SAN FELIPE DE ACONCAGUA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5253,13 +5253,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>859.95</v>
+        <v>16493.39</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3132-138-CM25</t>
+          <t>1943-172-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.950.800-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>16493.39</v>
+        <v>2931.66</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1943-172-CM25</t>
+          <t>2221-19-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.511.055-k</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE SAN FELIPE DE ACONCAGUA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2931.66</v>
+        <v>859.95</v>
       </c>
     </row>
     <row r="77">
@@ -5519,7 +5519,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1099899-56-CM25</t>
+          <t>4820-89-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5539,17 +5539,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1391.71</v>
+        <v>63418.24</v>
       </c>
     </row>
     <row r="80">
@@ -5649,7 +5649,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4820-89-CM25</t>
+          <t>3679-4875-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5669,17 +5669,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>63418.24</v>
+        <v>18731.04</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3679-4875-CM25</t>
+          <t>1099899-56-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>18731.04</v>
+        <v>1391.71</v>
       </c>
     </row>
     <row r="83">
@@ -6169,7 +6169,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>898-2577-CM25</t>
+          <t>2782-127-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6189,17 +6189,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>21003.76</v>
+        <v>1927.08</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2782-127-CM25</t>
+          <t>2782-128-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6293,13 +6293,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1927.08</v>
+        <v>2047.52</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2782-128-CM25</t>
+          <t>2782-129-CM25</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2047.52</v>
+        <v>1445.31</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2782-129-CM25</t>
+          <t>2782-131-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6429,7 +6429,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2782-131-CM25</t>
+          <t>2782-132-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1445.31</v>
+        <v>1806.64</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2782-132-CM25</t>
+          <t>2782-133-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1806.64</v>
+        <v>2047.52</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2782-133-CM25</t>
+          <t>898-2577-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6579,17 +6579,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>2047.52</v>
+        <v>21003.76</v>
       </c>
     </row>
     <row r="96">
@@ -6754,7 +6754,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>377-139-CM25</t>
+          <t>377-138-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>15399.51</v>
+        <v>22031.23</v>
       </c>
     </row>
     <row r="99">
@@ -6884,7 +6884,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>377-138-CM25</t>
+          <t>377-139-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>22031.23</v>
+        <v>15399.51</v>
       </c>
     </row>
     <row r="101">
@@ -7664,7 +7664,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>377-147-CM25</t>
+          <t>619133-14704-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>6473.04</v>
+        <v>25121.39</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3544-92-CM25</t>
+          <t>900-361-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.979.910-0</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1011.15</v>
+        <v>2523.98</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>619133-14704-CM25</t>
+          <t>4968-3280-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>25121.39</v>
+        <v>5486.92</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>900-361-CM25</t>
+          <t>3544-92-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.979.910-0</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2523.98</v>
+        <v>1011.15</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4968-3280-CM25</t>
+          <t>377-147-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>5486.92</v>
+        <v>6473.04</v>
       </c>
     </row>
     <row r="117">
@@ -8509,7 +8509,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1111432-263-CM25</t>
+          <t>2170-2474-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.287.560-5</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO SAN FELIPE</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8568,13 +8568,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>23416.28</v>
+        <v>18719.21</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2170-2474-CM25</t>
+          <t>1111432-263-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8599,12 +8599,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>69.287.560-5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>CONSULTORIO GENERAL URBANO SAN FELIPE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>18719.21</v>
+        <v>23416.28</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>377-168-CM25</t>
+          <t>3777-88-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1763.57</v>
+        <v>6048.34</v>
       </c>
     </row>
     <row r="128">
@@ -8769,7 +8769,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3777-88-CM25</t>
+          <t>377-168-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6048.34</v>
+        <v>1763.57</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>617807-4868-CM25</t>
+          <t>3232-197-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8854,17 +8854,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>14784.92</v>
+        <v>433.2</v>
       </c>
     </row>
     <row r="131">
@@ -8964,7 +8964,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3232-197-CM25</t>
+          <t>617807-4868-CM25</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8984,17 +8984,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>433.2</v>
+        <v>14784.92</v>
       </c>
     </row>
     <row r="133">
@@ -9094,7 +9094,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3544-107-CM25</t>
+          <t>1099899-80-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1586.6</v>
+        <v>1326.39</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>875646-3464-CM25</t>
+          <t>1099899-81-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.602.057-9</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hospital Dr. Eduardo Pereira Ramirez</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>67827</v>
+        <v>6300.37</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1099899-80-CM25</t>
+          <t>3544-107-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1326.39</v>
+        <v>1586.6</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1099899-81-CM25</t>
+          <t>898-2845-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9348,13 +9348,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>6300.37</v>
+        <v>21101.73</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>898-2845-CM25</t>
+          <t>875646-3464-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.602.057-9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>Hospital Dr. Eduardo Pereira Ramirez</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>21101.73</v>
+        <v>67827</v>
       </c>
     </row>
     <row r="139">
@@ -9484,7 +9484,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>4686-257-CM25</t>
+          <t>3244-1842-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9504,17 +9504,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>60.202.000-2</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cámara de Diputados de Chile</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>29822.01</v>
+        <v>4143.69</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3244-1842-CM25</t>
+          <t>4686-257-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9569,17 +9569,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>4143.69</v>
+        <v>29822.01</v>
       </c>
     </row>
     <row r="142">
@@ -9744,7 +9744,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>838108-100-CM25</t>
+          <t>2782-241-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9764,17 +9764,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>528.85</v>
+        <v>28072.43</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2782-241-CM25</t>
+          <t>838108-100-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9829,17 +9829,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>28072.43</v>
+        <v>528.85</v>
       </c>
     </row>
     <row r="146">
@@ -10199,7 +10199,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>619133-15182-CM25</t>
+          <t>2599-51-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10258,13 +10258,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>24587.26</v>
+        <v>8411.6</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2599-51-CM25</t>
+          <t>619133-15182-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10323,7 +10323,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>8411.6</v>
+        <v>24587.26</v>
       </c>
     </row>
     <row r="153">
@@ -10524,7 +10524,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4469-269-CM25</t>
+          <t>4469-268-CM25</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>938.14</v>
+        <v>214</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4469-268-CM25</t>
+          <t>4469-269-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>214</v>
+        <v>938.14</v>
       </c>
     </row>
     <row r="158">
@@ -10719,7 +10719,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4803-142-CM25</t>
+          <t>2594-443-CM25</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4457.82</v>
+        <v>1174.35</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2594-443-CM25</t>
+          <t>4803-142-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1174.35</v>
+        <v>4457.82</v>
       </c>
     </row>
     <row r="161">
@@ -12344,7 +12344,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3536-88-CM25</t>
+          <t>5909-11-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.101.025-7</t>
+          <t>61.102.076-7</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>10613.57</v>
+        <v>2352.04</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5909-11-CM25</t>
+          <t>3536-88-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.102.076-7</t>
+          <t>61.101.025-7</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2352.04</v>
+        <v>10613.57</v>
       </c>
     </row>
     <row r="186">
@@ -12994,7 +12994,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3544-171-CM25</t>
+          <t>3536-100-CM25</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.101.025-7</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3207.84</v>
+        <v>6415.67</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3530-75-CM25</t>
+          <t>3544-171-CM25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>61.943.600-8</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -13118,7 +13118,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>673.64</v>
+        <v>3207.84</v>
       </c>
     </row>
     <row r="196">
@@ -13319,7 +13319,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>3536-100-CM25</t>
+          <t>3530-75-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.101.025-7</t>
+          <t>61.943.600-8</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -13378,7 +13378,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>6415.67</v>
+        <v>673.64</v>
       </c>
     </row>
     <row r="200">
@@ -14164,7 +14164,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3333-249-CM25</t>
+          <t>1099899-119-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14184,17 +14184,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.061.200-3</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLMUE</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14223,13 +14223,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>7993.83</v>
+        <v>6533.06</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>898-3570-CM25</t>
+          <t>3333-249-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14249,17 +14249,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>69.061.200-3</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE OLMUE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>21320.03</v>
+        <v>7993.83</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1099899-120-CM25</t>
+          <t>2755-342-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14314,17 +14314,17 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14353,13 +14353,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1278.69</v>
+        <v>46551.39</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1099899-119-CM25</t>
+          <t>898-3570-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14418,13 +14418,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>6533.06</v>
+        <v>21320.03</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2755-342-CM25</t>
+          <t>1099899-120-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14444,17 +14444,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14483,13 +14483,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>46551.39</v>
+        <v>1278.69</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3446-186-CM25</t>
+          <t>1705-400-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14514,12 +14514,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14548,13 +14548,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2142.66</v>
+        <v>24828.32</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1705-400-CM25</t>
+          <t>3446-186-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14579,12 +14579,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14613,7 +14613,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>24828.32</v>
+        <v>2142.66</v>
       </c>
     </row>
     <row r="219">
@@ -15334,7 +15334,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2512-64-CM25</t>
+          <t>2594-619-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15354,17 +15354,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15393,13 +15393,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1402.35</v>
+        <v>301.58</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2594-619-CM25</t>
+          <t>2512-63-CM25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15419,17 +15419,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>301.58</v>
+        <v>1419.34</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2512-63-CM25</t>
+          <t>2512-64-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15523,7 +15523,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1419.34</v>
+        <v>1402.35</v>
       </c>
     </row>
     <row r="233">
@@ -16179,7 +16179,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>875646-4349-CM25</t>
+          <t>3530-83-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16204,12 +16204,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.602.057-9</t>
+          <t>61.943.600-8</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Hospital Dr. Eduardo Pereira Ramirez</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>67030.78</v>
+        <v>1567.97</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3530-83-CM25</t>
+          <t>875646-4349-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16269,12 +16269,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.943.600-8</t>
+          <t>61.602.057-9</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Hospital Dr. Eduardo Pereira Ramirez</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1567.97</v>
+        <v>67030.78</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>950-76-CM25</t>
+          <t>4469-566-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16329,17 +16329,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>60.901.007-K</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16368,13 +16368,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2450.6</v>
+        <v>597.86</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>619133-16732-CM25</t>
+          <t>4469-567-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16394,17 +16394,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5759.6</v>
+        <v>498.22</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>4469-566-CM25</t>
+          <t>619133-16732-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16459,17 +16459,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16498,13 +16498,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>597.86</v>
+        <v>5759.6</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>4469-567-CM25</t>
+          <t>950-76-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16524,17 +16524,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>60.901.007-K</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,7 +16563,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>498.22</v>
+        <v>2450.6</v>
       </c>
     </row>
     <row r="249">
@@ -16959,7 +16959,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3117-1032-CM25</t>
+          <t>2170-2835-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.102.006-6</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>3712.3</v>
+        <v>18338.75</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2170-2836-CM25</t>
+          <t>3117-1032-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17049,12 +17049,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.102.006-6</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2980.05</v>
+        <v>3712.3</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2170-2835-CM25</t>
+          <t>2170-2836-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17148,7 +17148,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>18338.75</v>
+        <v>2980.05</v>
       </c>
     </row>
     <row r="258">
@@ -17739,7 +17739,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3232-408-CM25</t>
+          <t>3530-95-CM25</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17764,12 +17764,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>61.943.600-8</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17798,13 +17798,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>21777.91</v>
+        <v>2074.09</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>3530-95-CM25</t>
+          <t>3232-408-CM25</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17829,12 +17829,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.943.600-8</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17863,13 +17863,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2074.09</v>
+        <v>21777.91</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1057379-1781-CM25</t>
+          <t>2186-787-CM25</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17894,12 +17894,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.606.703-6</t>
+          <t>61.606.607-2</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
+          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17928,13 +17928,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>144.2</v>
+        <v>4631.2</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2186-787-CM25</t>
+          <t>1057379-1781-CM25</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17959,12 +17959,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.606.607-2</t>
+          <t>61.606.703-6</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
+          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17993,13 +17993,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>4631.2</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3536-147-CM25</t>
+          <t>1057379-1786-CM25</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.101.025-7</t>
+          <t>61.606.703-6</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -18058,13 +18058,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2057.87</v>
+        <v>2956.9</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1057379-1786-CM25</t>
+          <t>3536-147-CM25</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18089,12 +18089,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>61.606.703-6</t>
+          <t>61.101.025-7</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -18123,7 +18123,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2956.9</v>
+        <v>2057.87</v>
       </c>
     </row>
     <row r="273">
@@ -18194,7 +18194,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>619133-17178-CM25</t>
+          <t>2755-419-CM25</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18214,17 +18214,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>25624.74</v>
+        <v>25738.06</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2755-419-CM25</t>
+          <t>619133-17178-CM25</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18279,17 +18279,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>25738.06</v>
+        <v>25624.74</v>
       </c>
     </row>
     <row r="276">
@@ -18389,7 +18389,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>898-4016-CM25</t>
+          <t>2755-420-CM25</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18409,17 +18409,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18448,13 +18448,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>20732.01</v>
+        <v>727.4400000000001</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3680-258-CM25</t>
+          <t>898-4016-CM25</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18474,17 +18474,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18513,13 +18513,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>696.26</v>
+        <v>20732.01</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2755-420-CM25</t>
+          <t>3680-258-CM25</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18544,12 +18544,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>727.4400000000001</v>
+        <v>696.26</v>
       </c>
     </row>
     <row r="280">
@@ -19039,7 +19039,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1057370-2396-CM25</t>
+          <t>2186-815-CM25</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>61.606.607-2</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,13 +19098,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>24491.68</v>
+        <v>3501.34</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2186-815-CM25</t>
+          <t>1057370-2396-CM25</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19129,12 +19129,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.606.607-2</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19163,13 +19163,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>3501.34</v>
+        <v>24491.68</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1953-1690-CM25</t>
+          <t>3515-462-CM25</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19228,7 +19228,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>310.69</v>
+        <v>1465.54</v>
       </c>
     </row>
     <row r="290">
@@ -19364,7 +19364,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>3515-462-CM25</t>
+          <t>1953-1690-CM25</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19389,12 +19389,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19423,7 +19423,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1465.54</v>
+        <v>310.69</v>
       </c>
     </row>
     <row r="293">
@@ -19884,7 +19884,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1099899-155-CM25</t>
+          <t>3632-132-CM25</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19904,17 +19904,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1252.95</v>
+        <v>13116.14</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>3632-132-CM25</t>
+          <t>1099899-156-CM25</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19969,17 +19969,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -20008,13 +20008,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>13116.14</v>
+        <v>6415.95</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1099899-156-CM25</t>
+          <t>1099899-155-CM25</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -20073,7 +20073,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>6415.95</v>
+        <v>1252.95</v>
       </c>
     </row>
     <row r="303">
@@ -20209,7 +20209,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>4968-4123-CM25</t>
+          <t>950-103-CM25</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20234,12 +20234,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>60.901.007-K</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20268,13 +20268,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3624.93</v>
+        <v>2958.02</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>4968-4122-CM25</t>
+          <t>4968-4123-CM25</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20333,13 +20333,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>3648.28</v>
+        <v>3624.93</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1705-548-CM25</t>
+          <t>4968-4122-CM25</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20364,12 +20364,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20398,13 +20398,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>23921.83</v>
+        <v>3648.28</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>950-103-CM25</t>
+          <t>1705-548-CM25</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20429,12 +20429,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>60.901.007-K</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20463,13 +20463,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2958.02</v>
+        <v>23921.83</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2594-851-CM25</t>
+          <t>2594-849-CM25</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>298.11</v>
+        <v>542.02</v>
       </c>
     </row>
     <row r="310">
@@ -20599,7 +20599,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2594-850-CM25</t>
+          <t>2594-851-CM25</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20658,13 +20658,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>668.49</v>
+        <v>298.11</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2594-849-CM25</t>
+          <t>2594-850-CM25</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20723,7 +20723,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>542.02</v>
+        <v>668.49</v>
       </c>
     </row>
     <row r="313">
@@ -23069,7 +23069,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1099899-178-CM25</t>
+          <t>1099899-177-CM25</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -23128,13 +23128,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1271.55</v>
+        <v>6401.24</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1099899-177-CM25</t>
+          <t>1099899-178-CM25</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23193,13 +23193,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>6401.24</v>
+        <v>1271.55</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>3680-369-CM25</t>
+          <t>3446-249-CM25</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23219,17 +23219,17 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23258,13 +23258,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>382.1</v>
+        <v>2076.65</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>3446-249-CM25</t>
+          <t>3680-369-CM25</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23284,17 +23284,17 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23323,7 +23323,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2076.65</v>
+        <v>382.1</v>
       </c>
     </row>
     <row r="353">
@@ -23524,7 +23524,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>3661-623-CM25</t>
+          <t>619133-24377-CM25</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23583,13 +23583,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>23929.93</v>
+        <v>24996.87</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>619133-24377-CM25</t>
+          <t>3661-623-CM25</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23614,12 +23614,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>24996.87</v>
+        <v>23929.93</v>
       </c>
     </row>
     <row r="358">
@@ -24304,7 +24304,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1057370-2538-CM25</t>
+          <t>1717-18-CM25</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24329,12 +24329,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>61.606.701-k</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>SERVICIO DE SALUD ACONCAGUA</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -24363,13 +24363,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>9074.280000000001</v>
+        <v>3964.4</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1717-18-CM25</t>
+          <t>1057370-2538-CM25</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24394,12 +24394,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.606.701-k</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24428,7 +24428,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>3964.4</v>
+        <v>9074.280000000001</v>
       </c>
     </row>
     <row r="370">
@@ -25279,7 +25279,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>3781-190-CM25</t>
+          <t>1705-705-CM25</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25304,12 +25304,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.102.008-2</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25338,13 +25338,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>38978.62</v>
+        <v>23324.22</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>950-153-CM25</t>
+          <t>3781-190-CM25</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25369,12 +25369,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>60.901.007-K</t>
+          <t>61.102.008-2</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25403,13 +25403,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>511.53</v>
+        <v>38978.62</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1099899-193-CM25</t>
+          <t>1099899-194-CM25</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25468,13 +25468,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1411.88</v>
+        <v>7192.27</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1705-705-CM25</t>
+          <t>950-153-CM25</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25499,12 +25499,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>60.901.007-K</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25533,13 +25533,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>23324.22</v>
+        <v>511.53</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1099899-194-CM25</t>
+          <t>1099899-193-CM25</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25598,13 +25598,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>7192.27</v>
+        <v>1411.88</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>4968-6969-CM25</t>
+          <t>1057379-1923-CM25</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25629,12 +25629,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.606.703-6</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25663,13 +25663,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1807.78</v>
+        <v>5444.27</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1170507-624-CM25</t>
+          <t>4968-6968-CM25</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25689,17 +25689,17 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>SERVICIO ELECTORAL</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25728,13 +25728,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>542.25</v>
+        <v>3886.01</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1057379-1923-CM25</t>
+          <t>1170507-624-CM25</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25754,17 +25754,17 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>61.606.703-6</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25793,13 +25793,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>5444.27</v>
+        <v>542.25</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>4968-6968-CM25</t>
+          <t>4968-6969-CM25</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25858,7 +25858,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>3886.01</v>
+        <v>1807.78</v>
       </c>
     </row>
     <row r="392">
@@ -26254,7 +26254,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>4820-328-CM25</t>
+          <t>2091-45-CM25</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26274,17 +26274,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>60.902.024-5</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>49503.41</v>
+        <v>633.21</v>
       </c>
     </row>
     <row r="399">
@@ -26384,7 +26384,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2091-45-CM25</t>
+          <t>4820-328-CM25</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26404,17 +26404,17 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>60.902.024-5</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26443,7 +26443,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>633.21</v>
+        <v>49503.41</v>
       </c>
     </row>
     <row r="401">
@@ -26514,7 +26514,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>4301-692-CM25</t>
+          <t>4686-732-CM25</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26539,12 +26539,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -26573,13 +26573,13 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>28034.22</v>
+        <v>60583.51</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>4686-732-CM25</t>
+          <t>899-879-CM25</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26599,17 +26599,17 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>60.202.000-2</t>
+          <t>61.602.067-6</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Cámara de Diputados de Chile</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -26638,13 +26638,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>60583.51</v>
+        <v>18023.6</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>899-879-CM25</t>
+          <t>4301-692-CM25</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26664,17 +26664,17 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>61.602.067-6</t>
+          <t>69.050.400-6</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -26703,7 +26703,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>18023.6</v>
+        <v>28034.22</v>
       </c>
     </row>
     <row r="405">
@@ -26904,7 +26904,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1108338-263-CM25</t>
+          <t>1943-642-CM25</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26929,12 +26929,12 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>69.287.570-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL N°2 DE LOS ANDES</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26963,7 +26963,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>15329.14</v>
+        <v>1761.76</v>
       </c>
     </row>
     <row r="409">
@@ -27034,7 +27034,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1943-642-CM25</t>
+          <t>1108338-263-CM25</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -27059,12 +27059,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.287.570-2</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CONSULTORIO GENERAL N°2 DE LOS ANDES</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -27093,7 +27093,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1761.76</v>
+        <v>15329.14</v>
       </c>
     </row>
     <row r="411">
@@ -27294,7 +27294,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>377-583-CM25</t>
+          <t>898-7196-CM25</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27314,17 +27314,17 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27353,13 +27353,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>17074.94</v>
+        <v>21233.12</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>898-7196-CM25</t>
+          <t>2170-3265-CM25</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27384,12 +27384,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27418,13 +27418,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>21233.12</v>
+        <v>3296.19</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2170-3265-CM25</t>
+          <t>2170-3266-CM25</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27483,13 +27483,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>3296.19</v>
+        <v>15166.51</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2170-3266-CM25</t>
+          <t>377-583-CM25</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27509,17 +27509,17 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -27548,7 +27548,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>15166.51</v>
+        <v>17074.94</v>
       </c>
     </row>
     <row r="418">
@@ -27619,7 +27619,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1099899-212-CM25</t>
+          <t>1099899-211-CM25</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -27678,13 +27678,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>1302.19</v>
+        <v>6623.23</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1170507-742-CM25</t>
+          <t>1099899-212-CM25</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27709,12 +27709,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>SERVICIO ELECTORAL</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27743,13 +27743,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>547.86</v>
+        <v>1302.19</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>956-1222-CM25</t>
+          <t>1170507-742-CM25</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27774,12 +27774,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>61.606.500-9</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27808,13 +27808,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1716377.79</v>
+        <v>547.86</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>4469-1339-CM25</t>
+          <t>956-1222-CM25</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27834,17 +27834,17 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>61.606.500-9</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -27873,13 +27873,13 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>153.08</v>
+        <v>1716377.79</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1099899-211-CM25</t>
+          <t>4469-1339-CM25</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27899,17 +27899,17 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -27938,7 +27938,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>6623.23</v>
+        <v>153.08</v>
       </c>
     </row>
     <row r="424">
@@ -28984,7 +28984,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>1111432-722-CM25</t>
+          <t>2200-437-CM25</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -29009,12 +29009,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>69.287.560-5</t>
+          <t>61.606.700-1</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO SAN FELIPE</t>
+          <t>SERVICIO DE SALUD ACONCAGUA</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -29043,13 +29043,13 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>43867.36</v>
+        <v>711451.9300000001</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2200-437-CM25</t>
+          <t>1111432-722-CM25</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>61.606.700-1</t>
+          <t>69.287.560-5</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>CONSULTORIO GENERAL URBANO SAN FELIPE</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -29108,7 +29108,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>711451.9300000001</v>
+        <v>43867.36</v>
       </c>
     </row>
     <row r="442">
@@ -29439,7 +29439,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>3680-539-CM25</t>
+          <t>1943-740-CM25</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -29459,17 +29459,17 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -29498,13 +29498,13 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>21474.53</v>
+        <v>627.11</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>1943-740-CM25</t>
+          <t>3680-539-CM25</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -29524,17 +29524,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -29563,7 +29563,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>627.11</v>
+        <v>21474.53</v>
       </c>
     </row>
     <row r="449">
@@ -29894,7 +29894,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>1057374-698-CM25</t>
+          <t>4686-844-CM25</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29914,17 +29914,17 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>61.602.042-0</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -29953,13 +29953,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>14910.57</v>
+        <v>59513.26</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>4686-844-CM25</t>
+          <t>1057374-698-CM25</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -29979,17 +29979,17 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>60.202.000-2</t>
+          <t>61.602.042-0</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>Cámara de Diputados de Chile</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -30018,7 +30018,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>59513.26</v>
+        <v>14910.57</v>
       </c>
     </row>
     <row r="456">
@@ -31389,7 +31389,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>838794-10-CM26</t>
+          <t>838794-9-CM26</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -31448,13 +31448,13 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>3570.41</v>
+        <v>9365</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>838794-9-CM26</t>
+          <t>838794-10-CM26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -31513,7 +31513,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>9365</v>
+        <v>3570.41</v>
       </c>
     </row>
     <row r="479">
@@ -31779,7 +31779,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>3217-4-CM26</t>
+          <t>2170-62-CM26</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -31804,12 +31804,12 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>61.102.008-2</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -31838,13 +31838,13 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>25013.99</v>
+        <v>9157.309999999999</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2170-61-CM26</t>
+          <t>1057374-56-CM26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -31869,12 +31869,12 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.602.042-0</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -31903,13 +31903,13 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>23282.69</v>
+        <v>13141.88</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2170-62-CM26</t>
+          <t>3217-4-CM26</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -31934,12 +31934,12 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.102.008-2</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -31968,13 +31968,13 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>9157.309999999999</v>
+        <v>25013.99</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>1057374-56-CM26</t>
+          <t>2170-61-CM26</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -31999,12 +31999,12 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>61.602.042-0</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -32033,13 +32033,13 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>13141.88</v>
+        <v>23282.69</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>3117-171-CM26</t>
+          <t>3047-24-CM26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -32059,12 +32059,12 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>61.102.006-6</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -32098,13 +32098,13 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>23924.94</v>
+        <v>2330.85</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>3047-24-CM26</t>
+          <t>3117-171-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -32124,12 +32124,12 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>61.102.006-6</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -32163,13 +32163,13 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>2330.85</v>
+        <v>23924.94</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>813685-8-CM26</t>
+          <t>1099899-11-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -32194,12 +32194,12 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -32228,13 +32228,13 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>75876.13</v>
+        <v>1532.82</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>4968-155-CM26</t>
+          <t>813685-8-CM26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -32259,12 +32259,12 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -32293,13 +32293,13 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1586.87</v>
+        <v>75876.13</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>4968-156-CM26</t>
+          <t>4968-155-CM26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -32358,13 +32358,13 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>4257.56</v>
+        <v>1586.87</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>1099899-10-CM26</t>
+          <t>4968-156-CM26</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -32389,12 +32389,12 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -32423,13 +32423,13 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>7683</v>
+        <v>4257.56</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>1099899-11-CM26</t>
+          <t>1099899-10-CM26</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -32488,7 +32488,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1532.82</v>
+        <v>7683</v>
       </c>
     </row>
     <row r="494">
@@ -33339,7 +33339,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>1057370-131-CM26</t>
+          <t>813685-13-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -33364,12 +33364,12 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>18248.8</v>
+        <v>11657.21</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>813685-13-CM26</t>
+          <t>1057370-131-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33429,12 +33429,12 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -33463,13 +33463,13 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>11657.21</v>
+        <v>18248.8</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>1099402-96-CM26</t>
+          <t>1705-140-CM26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -33494,12 +33494,12 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>62.000.620-3</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -33528,13 +33528,13 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>15479.11</v>
+        <v>23111.77</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>1705-140-CM26</t>
+          <t>1099402-96-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33559,12 +33559,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>62.000.620-3</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -33593,7 +33593,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>23111.77</v>
+        <v>15479.11</v>
       </c>
     </row>
     <row r="511">
@@ -33729,7 +33729,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2170-182-CM26</t>
+          <t>2170-183-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -33788,13 +33788,13 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>25664.2</v>
+        <v>3860.94</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2170-183-CM26</t>
+          <t>2170-184-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -33853,13 +33853,13 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>3860.94</v>
+        <v>386.09</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2170-184-CM26</t>
+          <t>2170-185-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -33918,13 +33918,13 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>386.09</v>
+        <v>4929.31</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2170-185-CM26</t>
+          <t>1099899-50-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33949,12 +33949,12 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -33983,13 +33983,13 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>4929.31</v>
+        <v>7344.16</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>1099899-50-CM26</t>
+          <t>2170-182-CM26</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -34014,12 +34014,12 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -34048,7 +34048,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>7344.16</v>
+        <v>25664.2</v>
       </c>
     </row>
     <row r="518">
@@ -34444,7 +34444,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>4968-389-CM26</t>
+          <t>2512-5-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -34469,12 +34469,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -34503,13 +34503,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>170.36</v>
+        <v>357.2</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2512-5-CM26</t>
+          <t>4968-388-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34534,12 +34534,12 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -34568,13 +34568,13 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>357.2</v>
+        <v>3918.25</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2512-6-CM26</t>
+          <t>4968-389-CM26</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -34599,12 +34599,12 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -34633,7 +34633,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>401.85</v>
+        <v>170.36</v>
       </c>
     </row>
     <row r="527">
@@ -34704,7 +34704,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>4968-388-CM26</t>
+          <t>2512-6-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -34729,12 +34729,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -34763,7 +34763,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>3918.25</v>
+        <v>401.85</v>
       </c>
     </row>
     <row r="529">
@@ -35419,7 +35419,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>3446-55-CM26</t>
+          <t>2755-80-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -35444,12 +35444,12 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -35478,7 +35478,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>4367.96</v>
+        <v>2511.58</v>
       </c>
     </row>
     <row r="540">
@@ -35549,7 +35549,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2755-80-CM26</t>
+          <t>3446-55-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -35574,12 +35574,12 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -35608,7 +35608,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>2511.58</v>
+        <v>4367.96</v>
       </c>
     </row>
     <row r="542">
@@ -35679,7 +35679,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>1705-218-CM26</t>
+          <t>1702-197-CM26</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -35704,12 +35704,12 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>61.606.605-6</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -35738,13 +35738,13 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>22745.92</v>
+        <v>32493.91</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>1702-197-CM26</t>
+          <t>1705-218-CM26</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -35769,12 +35769,12 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>61.606.605-6</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -35803,13 +35803,13 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>32493.91</v>
+        <v>22745.92</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2170-313-CM26</t>
+          <t>2170-315-CM26</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -35868,13 +35868,13 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>15536.21</v>
+        <v>357.57</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2170-314-CM26</t>
+          <t>2170-316-CM26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -35933,13 +35933,13 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>3575.65</v>
+        <v>4565.09</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2170-315-CM26</t>
+          <t>2170-314-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35998,13 +35998,13 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>357.57</v>
+        <v>3575.65</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2170-316-CM26</t>
+          <t>2170-313-CM26</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -36063,7 +36063,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>4565.09</v>
+        <v>15536.21</v>
       </c>
     </row>
     <row r="549">
@@ -36134,7 +36134,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>1099899-62-CM26</t>
+          <t>1099899-63-CM26</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -36193,13 +36193,13 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>28017.54</v>
+        <v>5405.87</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>1099899-63-CM26</t>
+          <t>1099899-62-CM26</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -36258,13 +36258,13 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>5405.87</v>
+        <v>28017.54</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>3544-66-CM26</t>
+          <t>3446-41-CM26</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -36289,7 +36289,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -36323,13 +36323,13 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1078.74</v>
+        <v>10782.14</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>3446-41-CM26</t>
+          <t>3544-66-CM26</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -36354,7 +36354,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
@@ -36388,7 +36388,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>10782.14</v>
+        <v>1078.74</v>
       </c>
     </row>
     <row r="554">
@@ -36459,7 +36459,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>898-1182-CM26</t>
+          <t>1057370-209-CM26</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -36484,12 +36484,12 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -36518,13 +36518,13 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>21815.92</v>
+        <v>12362.35</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1057370-209-CM26</t>
+          <t>898-1182-CM26</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -36549,12 +36549,12 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -36583,7 +36583,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>12362.35</v>
+        <v>21815.92</v>
       </c>
     </row>
     <row r="557">
@@ -36719,7 +36719,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>4968-536-CM26</t>
+          <t>3446-46-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -36744,12 +36744,12 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -36778,13 +36778,13 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>2746.48</v>
+        <v>954.7</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>3446-46-CM26</t>
+          <t>4968-535-CM26</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -36809,12 +36809,12 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -36843,13 +36843,13 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>954.7</v>
+        <v>4059.4</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>4968-535-CM26</t>
+          <t>4968-536-CM26</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -36908,13 +36908,13 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>4059.4</v>
+        <v>2746.48</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>707419-33-CM26</t>
+          <t>3446-73-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -36934,17 +36934,17 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -36973,7 +36973,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>4911.1</v>
+        <v>1127.43</v>
       </c>
     </row>
     <row r="563">
@@ -37044,7 +37044,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>3446-73-CM26</t>
+          <t>707419-33-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -37064,17 +37064,17 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -37103,13 +37103,13 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>1127.43</v>
+        <v>4911.1</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>3446-91-CM26</t>
+          <t>619133-2112-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -37134,12 +37134,12 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -37168,13 +37168,13 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1128.55</v>
+        <v>29228.62</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>619133-2112-CM26</t>
+          <t>3446-91-CM26</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -37199,12 +37199,12 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -37233,13 +37233,13 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>29228.62</v>
+        <v>1128.55</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>1953-653-CM26</t>
+          <t>4469-189-CM26</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -37259,17 +37259,17 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -37298,13 +37298,13 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>307.58</v>
+        <v>268.03</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>4469-189-CM26</t>
+          <t>1953-653-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -37324,17 +37324,17 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -37363,13 +37363,13 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>268.03</v>
+        <v>307.58</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>4686-284-CM26</t>
+          <t>2755-129-CM26</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -37389,17 +37389,17 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>60.202.000-2</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>Cámara de Diputados de Chile</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -37428,13 +37428,13 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>32341.53</v>
+        <v>1134.79</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2755-129-CM26</t>
+          <t>4686-284-CM26</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -37454,17 +37454,17 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -37493,7 +37493,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>1134.79</v>
+        <v>32341.53</v>
       </c>
     </row>
     <row r="571">
@@ -37564,7 +37564,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>1705-279-CM26</t>
+          <t>2170-411-CM26</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -37589,12 +37589,12 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -37623,13 +37623,13 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>24579.57</v>
+        <v>21325.57</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2170-411-CM26</t>
+          <t>2170-412-CM26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -37688,13 +37688,13 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>21325.57</v>
+        <v>8829</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2170-412-CM26</t>
+          <t>1705-279-CM26</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -37719,12 +37719,12 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -37753,7 +37753,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>8829</v>
+        <v>24579.57</v>
       </c>
     </row>
     <row r="575">
@@ -37824,7 +37824,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>4469-245-CM26</t>
+          <t>3047-193-CM26</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -37844,17 +37844,17 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -37883,13 +37883,13 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>4505.99</v>
+        <v>167.3</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>3047-193-CM26</t>
+          <t>1099402-201-CM26</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>62.000.620-3</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -37948,13 +37948,13 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>167.3</v>
+        <v>13358.93</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>1099402-201-CM26</t>
+          <t>945256-26-CM26</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -37979,12 +37979,12 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>62.000.620-3</t>
+          <t>61.980.790-1</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -38013,13 +38013,13 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>13358.93</v>
+        <v>1674.05</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>1099834-60-CM26</t>
+          <t>4469-245-CM26</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -38039,17 +38039,17 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>62.000.640-8</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -38078,13 +38078,13 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>8928.27</v>
+        <v>4505.99</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>3047-194-CM26</t>
+          <t>4469-246-CM26</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -38104,17 +38104,17 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -38143,13 +38143,13 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2231.79</v>
+        <v>530.12</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>945256-26-CM26</t>
+          <t>3047-194-CM26</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -38174,12 +38174,12 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>61.980.790-1</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -38208,13 +38208,13 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>1674.05</v>
+        <v>2231.79</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>4469-246-CM26</t>
+          <t>1099834-60-CM26</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -38234,17 +38234,17 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>62.000.640-8</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -38273,13 +38273,13 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>530.12</v>
+        <v>8928.27</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>3544-71-CM26</t>
+          <t>1702-260-CM26</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -38304,12 +38304,12 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.606.605-6</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -38338,7 +38338,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>1663.41</v>
+        <v>38751.44</v>
       </c>
     </row>
     <row r="584">
@@ -38409,7 +38409,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>1702-260-CM26</t>
+          <t>3544-71-CM26</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -38434,12 +38434,12 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>61.606.605-6</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -38468,7 +38468,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>38751.44</v>
+        <v>1663.41</v>
       </c>
     </row>
     <row r="586">
@@ -38539,7 +38539,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>4968-684-CM26</t>
+          <t>1057370-262-CM26</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -38564,12 +38564,12 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -38598,13 +38598,13 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>2432.42</v>
+        <v>13735.42</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>1057370-262-CM26</t>
+          <t>4968-683-CM26</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -38629,12 +38629,12 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -38663,13 +38663,13 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>13735.42</v>
+        <v>3992.01</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>4968-683-CM26</t>
+          <t>4968-684-CM26</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -38728,13 +38728,13 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>3992.01</v>
+        <v>2432.42</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>3446-99-CM26</t>
+          <t>1057374-246-CM26</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -38759,12 +38759,12 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>61.602.042-0</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -38793,13 +38793,13 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>1680.05</v>
+        <v>15748.22</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>1057374-246-CM26</t>
+          <t>3446-99-CM26</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -38824,12 +38824,12 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>61.602.042-0</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -38858,7 +38858,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>15748.22</v>
+        <v>1680.05</v>
       </c>
     </row>
     <row r="592">
@@ -38994,7 +38994,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>619133-2526-CM26</t>
+          <t>1943-159-CM26</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -39019,12 +39019,12 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -39053,13 +39053,13 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>27000.82</v>
+        <v>2686.36</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>1943-159-CM26</t>
+          <t>619133-2526-CM26</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -39084,12 +39084,12 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -39118,13 +39118,13 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>2686.36</v>
+        <v>27000.82</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>838108-169-CM26</t>
+          <t>1943-158-CM26</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -39149,12 +39149,12 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -39183,13 +39183,13 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>1111.13</v>
+        <v>3800.38</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>1943-158-CM26</t>
+          <t>838108-169-CM26</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -39214,12 +39214,12 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -39248,7 +39248,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>3800.38</v>
+        <v>1111.13</v>
       </c>
     </row>
     <row r="598">
@@ -39319,7 +39319,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>619133-2712-CM26</t>
+          <t>4968-760-CM26</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -39344,12 +39344,12 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -39378,7 +39378,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>459.45</v>
+        <v>3982.56</v>
       </c>
     </row>
     <row r="600">
@@ -39449,7 +39449,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>4968-760-CM26</t>
+          <t>619133-2712-CM26</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -39474,12 +39474,12 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -39508,7 +39508,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>3982.56</v>
+        <v>459.45</v>
       </c>
     </row>
     <row r="602">
@@ -39839,7 +39839,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>1705-354-CM26</t>
+          <t>4469-368-CM26</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -39859,17 +39859,17 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -39898,13 +39898,13 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>23472.53</v>
+        <v>383.92</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>1079516-520-CM26</t>
+          <t>1079516-521-CM26</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -39963,13 +39963,13 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>45503.2</v>
+        <v>71400.52</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>1079516-521-CM26</t>
+          <t>1099402-248-CM26</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -39994,12 +39994,12 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>62.000.620-3</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -40028,13 +40028,13 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>71400.52</v>
+        <v>13803.97</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>1079516-522-CM26</t>
+          <t>1705-354-CM26</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -40059,12 +40059,12 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -40093,13 +40093,13 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>70244.17</v>
+        <v>23472.53</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>4469-368-CM26</t>
+          <t>1111432-326-CM26</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -40119,17 +40119,17 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>69.287.560-5</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>CONSULTORIO GENERAL URBANO SAN FELIPE</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -40158,13 +40158,13 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>383.92</v>
+        <v>38021.56</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>1099402-248-CM26</t>
+          <t>1079516-520-CM26</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -40189,12 +40189,12 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>62.000.620-3</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -40223,13 +40223,13 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>13803.97</v>
+        <v>45503.2</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>1111432-326-CM26</t>
+          <t>1079516-522-CM26</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -40254,12 +40254,12 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>69.287.560-5</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO SAN FELIPE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -40288,7 +40288,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>38021.56</v>
+        <v>70244.17</v>
       </c>
     </row>
     <row r="614">
@@ -41204,7 +41204,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>619133-3106-CM26</t>
+          <t>2755-208-CM26</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -41229,12 +41229,12 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -41263,7 +41263,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>27819.02</v>
+        <v>25896.02</v>
       </c>
     </row>
     <row r="629">
@@ -41334,7 +41334,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2755-208-CM26</t>
+          <t>619133-3106-CM26</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -41359,12 +41359,12 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -41393,13 +41393,13 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>25896.02</v>
+        <v>27819.02</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>1079516-604-CM26</t>
+          <t>1079516-603-CM26</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -41458,13 +41458,13 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>82020.28999999999</v>
+        <v>74684.81</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>1079516-603-CM26</t>
+          <t>1079516-604-CM26</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -41523,13 +41523,13 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>74684.81</v>
+        <v>82020.28999999999</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2200-214-CM26</t>
+          <t>2755-210-CM26</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -41554,12 +41554,12 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>61.606.700-1</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -41588,13 +41588,13 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>78640.2</v>
+        <v>22243.94</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>3544-119-CM26</t>
+          <t>2200-214-CM26</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -41619,12 +41619,12 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.606.700-1</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ACONCAGUA</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -41653,13 +41653,13 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>1685.15</v>
+        <v>78640.2</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2755-210-CM26</t>
+          <t>3544-119-CM26</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -41684,12 +41684,12 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -41718,7 +41718,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>22243.94</v>
+        <v>1685.15</v>
       </c>
     </row>
     <row r="636">
@@ -41789,7 +41789,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>4469-481-CM26</t>
+          <t>4469-482-CM26</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -41848,13 +41848,13 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>1182.85</v>
+        <v>1075.32</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>4469-482-CM26</t>
+          <t>4469-481-CM26</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -41913,7 +41913,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>1075.32</v>
+        <v>1182.85</v>
       </c>
     </row>
     <row r="639">
@@ -42179,7 +42179,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>3111-21-CM26</t>
+          <t>4968-971-CM26</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -42204,12 +42204,12 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>61.966.600-3</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -42238,13 +42238,13 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>11486.62</v>
+        <v>4046.3</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>4968-971-CM26</t>
+          <t>4968-972-CM26</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -42303,13 +42303,13 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>4046.3</v>
+        <v>6711.14</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>4968-972-CM26</t>
+          <t>1705-425-CM26</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -42334,12 +42334,12 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>6711.14</v>
+        <v>23876.4</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>1705-425-CM26</t>
+          <t>3111-21-CM26</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -42399,12 +42399,12 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>61.966.600-3</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -42433,13 +42433,13 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>23876.4</v>
+        <v>11486.62</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>1099834-79-CM26</t>
+          <t>898-2154-CM26</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -42464,12 +42464,12 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>62.000.640-8</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -42498,13 +42498,13 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>5452.74</v>
+        <v>20720.42</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>898-2154-CM26</t>
+          <t>617807-3650-CM26</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -42524,17 +42524,17 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -42563,13 +42563,13 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>20720.42</v>
+        <v>20453.6</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>617807-3650-CM26</t>
+          <t>1099834-79-CM26</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -42589,17 +42589,17 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>62.000.640-8</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -42628,7 +42628,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>20453.6</v>
+        <v>5452.74</v>
       </c>
     </row>
     <row r="650">
@@ -43024,7 +43024,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>3544-156-CM26</t>
+          <t>1422825-1215-CM26</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -43049,12 +43049,12 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -43083,13 +43083,13 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>1068.71</v>
+        <v>74809.5</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>1422825-1215-CM26</t>
+          <t>3544-156-CM26</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -43114,12 +43114,12 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -43148,7 +43148,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>74809.5</v>
+        <v>1068.71</v>
       </c>
     </row>
     <row r="658">
@@ -43674,7 +43674,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>1943-233-CM26</t>
+          <t>742475-60-CM26</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -43694,17 +43694,17 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -43714,12 +43714,12 @@
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
@@ -43733,13 +43733,13 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>192.74</v>
+        <v>10774.53</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>742475-60-CM26</t>
+          <t>1943-233-CM26</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -43759,17 +43759,17 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -43779,12 +43779,12 @@
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
@@ -43798,7 +43798,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>10774.53</v>
+        <v>192.74</v>
       </c>
     </row>
     <row r="668">
@@ -43869,7 +43869,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>2170-712-CM26</t>
+          <t>2170-711-CM26</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -43928,7 +43928,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>8737.549999999999</v>
+        <v>23326.21</v>
       </c>
     </row>
     <row r="670">
@@ -44064,7 +44064,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>2170-711-CM26</t>
+          <t>2170-712-CM26</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -44123,7 +44123,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>23326.21</v>
+        <v>8737.549999999999</v>
       </c>
     </row>
     <row r="673">
@@ -44454,7 +44454,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>2186-649-CM26</t>
+          <t>377-322-CM26</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -44479,12 +44479,12 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>61.606.607-2</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -44513,13 +44513,13 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>12257.15</v>
+        <v>23561.59</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>377-322-CM26</t>
+          <t>3544-176-CM26</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -44544,12 +44544,12 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
@@ -44578,7 +44578,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>23561.59</v>
+        <v>1592.48</v>
       </c>
     </row>
     <row r="680">
@@ -44649,7 +44649,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>3544-176-CM26</t>
+          <t>2186-649-CM26</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -44674,12 +44674,12 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.606.607-2</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -44708,7 +44708,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>1592.48</v>
+        <v>12257.15</v>
       </c>
     </row>
     <row r="682">
@@ -44779,7 +44779,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>898-2419-CM26</t>
+          <t>1099834-88-CM26</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -44804,12 +44804,12 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>62.000.640-8</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -44838,7 +44838,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>20308.48</v>
+        <v>12826.41</v>
       </c>
     </row>
     <row r="684">
@@ -44909,7 +44909,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>1099834-88-CM26</t>
+          <t>898-2419-CM26</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -44934,12 +44934,12 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>62.000.640-8</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -44968,13 +44968,13 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>12826.41</v>
+        <v>20308.48</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>1099899-129-CM26</t>
+          <t>1099899-128-CM26</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -45033,13 +45033,13 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>7961.19</v>
+        <v>1485.93</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>1099899-128-CM26</t>
+          <t>1099899-129-CM26</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -45098,13 +45098,13 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>1485.93</v>
+        <v>7961.19</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>617807-4319-CM26</t>
+          <t>2626-391-CM26</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -45129,12 +45129,12 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>69.050.700-5</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE PUTAENDO</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -45163,13 +45163,13 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>17977.29</v>
+        <v>22115.2</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>2626-391-CM26</t>
+          <t>617807-4319-CM26</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -45194,12 +45194,12 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>69.050.700-5</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUTAENDO</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -45228,7 +45228,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>22115.2</v>
+        <v>17977.29</v>
       </c>
     </row>
     <row r="690">
@@ -45819,7 +45819,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>898-2709-CM26</t>
+          <t>617807-4626-CM26</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -45844,12 +45844,12 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -45878,7 +45878,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>22996.06</v>
+        <v>17096.88</v>
       </c>
     </row>
     <row r="700">
@@ -45949,7 +45949,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>617807-4626-CM26</t>
+          <t>898-2709-CM26</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -45974,12 +45974,12 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -46008,13 +46008,13 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>17096.88</v>
+        <v>22996.06</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>3515-372-CM26</t>
+          <t>617807-4651-CM26</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -46034,17 +46034,17 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -46073,13 +46073,13 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>1533.15</v>
+        <v>1458.49</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>617807-4651-CM26</t>
+          <t>3515-372-CM26</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -46099,17 +46099,17 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -46138,7 +46138,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>1458.49</v>
+        <v>1533.15</v>
       </c>
     </row>
     <row r="704">
@@ -46339,7 +46339,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>1422825-1409-CM26</t>
+          <t>1943-292-CM26</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -46364,12 +46364,12 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -46398,13 +46398,13 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>1817330.45</v>
+        <v>4772.84</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>1943-292-CM26</t>
+          <t>1422825-1409-CM26</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -46429,12 +46429,12 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -46463,13 +46463,13 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>4772.84</v>
+        <v>1817330.45</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>3544-205-CM26</t>
+          <t>3544-201-CM26</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -46528,13 +46528,13 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>470.13</v>
+        <v>1639.99</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>3544-201-CM26</t>
+          <t>3544-205-CM26</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -46593,13 +46593,13 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>1639.99</v>
+        <v>470.13</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2170-869-CM26</t>
+          <t>1705-549-CM26</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -46624,12 +46624,12 @@
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -46658,13 +46658,13 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>23878.25</v>
+        <v>25235.07</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>1705-549-CM26</t>
+          <t>2170-869-CM26</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -46689,12 +46689,12 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -46723,7 +46723,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>25235.07</v>
+        <v>23878.25</v>
       </c>
     </row>
     <row r="713">
@@ -46794,7 +46794,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2186-754-CM26</t>
+          <t>3515-387-CM26</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -46814,17 +46814,17 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>61.606.607-2</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -46853,13 +46853,13 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>15872.37</v>
+        <v>1088.83</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>3515-387-CM26</t>
+          <t>2186-754-CM26</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -46879,17 +46879,17 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.606.607-2</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -46918,13 +46918,13 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>1088.83</v>
+        <v>15872.37</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>4469-815-CM26</t>
+          <t>1702-559-CM26</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -46944,17 +46944,17 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>61.606.605-6</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -46983,7 +46983,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>1482.84</v>
+        <v>21615.78</v>
       </c>
     </row>
     <row r="717">
@@ -47054,7 +47054,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>1702-559-CM26</t>
+          <t>4469-815-CM26</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -47074,17 +47074,17 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>61.606.605-6</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -47113,7 +47113,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>21615.78</v>
+        <v>1482.84</v>
       </c>
     </row>
     <row r="719">
@@ -47184,7 +47184,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>1099899-138-CM26</t>
+          <t>1099899-137-CM26</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -47243,13 +47243,13 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>7454.57</v>
+        <v>1412.76</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>1099899-137-CM26</t>
+          <t>1099899-138-CM26</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -47308,7 +47308,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>1412.76</v>
+        <v>7454.57</v>
       </c>
     </row>
     <row r="722">
@@ -47509,7 +47509,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>1057370-518-CM26</t>
+          <t>2626-441-CM26</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -47534,12 +47534,12 @@
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>69.050.700-5</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>I MUNICIPALIDAD DE PUTAENDO</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -47568,7 +47568,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>13742.49</v>
+        <v>2475.72</v>
       </c>
     </row>
     <row r="726">
@@ -47704,7 +47704,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>2626-441-CM26</t>
+          <t>1057370-518-CM26</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -47729,12 +47729,12 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>69.050.700-5</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUTAENDO</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -47763,7 +47763,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>2475.72</v>
+        <v>13742.49</v>
       </c>
     </row>
     <row r="729">
@@ -47834,7 +47834,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>838108-262-CM26</t>
+          <t>1195104-234-CM26</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -47859,12 +47859,12 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>62.000.920-2</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -47893,13 +47893,13 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>910.16</v>
+        <v>7884.28</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>1195104-234-CM26</t>
+          <t>838108-262-CM26</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -47924,12 +47924,12 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>62.000.920-2</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -47958,13 +47958,13 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>7884.28</v>
+        <v>910.16</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>1057374-432-CM26</t>
+          <t>4968-1359-CM26</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -47989,12 +47989,12 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>61.602.042-0</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -48023,13 +48023,13 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>15776.8</v>
+        <v>7882.93</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>4968-1359-CM26</t>
+          <t>1057374-432-CM26</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -48054,12 +48054,12 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.602.042-0</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -48088,13 +48088,13 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>7882.93</v>
+        <v>15776.8</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>619133-4826-CM26</t>
+          <t>898-3074-CM26</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -48114,17 +48114,17 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>61.602.038-2</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -48153,7 +48153,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>28812.84</v>
+        <v>22407.89</v>
       </c>
     </row>
     <row r="735">
@@ -48224,7 +48224,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>898-3074-CM26</t>
+          <t>4776-518-CM26</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -48244,17 +48244,17 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.108.000-k</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -48283,13 +48283,13 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>22407.89</v>
+        <v>2660.49</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>4776-518-CM26</t>
+          <t>619133-4826-CM26</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -48314,12 +48314,12 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>61.108.000-k</t>
+          <t>61.602.038-2</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
+          <t>SERVICIO SALUD SAN FELIPE LOS ANDES HOSP</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -48348,7 +48348,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>2660.49</v>
+        <v>28812.84</v>
       </c>
     </row>
     <row r="738">
@@ -48614,7 +48614,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2512-27-CM26</t>
+          <t>2512-26-CM26</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -48679,7 +48679,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2512-26-CM26</t>
+          <t>2512-27-CM26</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -48874,7 +48874,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>4820-207-CM26</t>
+          <t>2170-948-CM26</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -48894,17 +48894,17 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -48933,13 +48933,13 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>73953.24000000001</v>
+        <v>8497.200000000001</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>4803-234-CM26</t>
+          <t>1705-624-CM26</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -48959,17 +48959,17 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>60.201.000-7</t>
+          <t>61.606.603-k</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>SENADO DE LA REPUBLICA</t>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -48998,13 +48998,13 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>4698.56</v>
+        <v>23973.57</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2170-948-CM26</t>
+          <t>4820-207-CM26</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -49024,17 +49024,17 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -49063,13 +49063,13 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>8497.200000000001</v>
+        <v>73953.24000000001</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>1705-624-CM26</t>
+          <t>4803-234-CM26</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -49089,17 +49089,17 @@
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>61.606.603-k</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -49128,7 +49128,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>23973.57</v>
+        <v>4698.56</v>
       </c>
     </row>
     <row r="750">
@@ -49199,7 +49199,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>1099402-506-CM26</t>
+          <t>1079516-1016-CM26</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -49224,12 +49224,12 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>62.000.620-3</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -49239,12 +49239,12 @@
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K751" t="inlineStr">
@@ -49258,13 +49258,13 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>13214.4</v>
+        <v>11606.31</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>1079516-1020-CM26</t>
+          <t>1079516-1017-CM26</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -49323,7 +49323,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>13588.47</v>
+        <v>8339.299999999999</v>
       </c>
     </row>
     <row r="753">
@@ -49394,7 +49394,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>1079516-1017-CM26</t>
+          <t>1079516-1019-CM26</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -49453,13 +49453,13 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>8339.299999999999</v>
+        <v>15622.47</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>1079516-1016-CM26</t>
+          <t>1079516-1020-CM26</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -49518,13 +49518,13 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>11606.31</v>
+        <v>13588.47</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>1079516-1015-CM26</t>
+          <t>1099402-506-CM26</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -49549,12 +49549,12 @@
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>62.000.620-3</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -49564,12 +49564,12 @@
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K756" t="inlineStr">
@@ -49583,13 +49583,13 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>29970.25</v>
+        <v>13214.4</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>1079516-1019-CM26</t>
+          <t>1079516-1015-CM26</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -49648,13 +49648,13 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>15622.47</v>
+        <v>29970.25</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>3047-527-CM26</t>
+          <t>1057379-496-CM26</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -49679,12 +49679,12 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>61.606.703-6</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
@@ -49713,7 +49713,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>9295.700000000001</v>
+        <v>9499.34</v>
       </c>
     </row>
     <row r="759">
@@ -49784,7 +49784,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>1057379-496-CM26</t>
+          <t>3047-527-CM26</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -49809,12 +49809,12 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>61.606.703-6</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA HOSPITAL DE PUTAENDO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
@@ -49843,7 +49843,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>9499.34</v>
+        <v>9295.700000000001</v>
       </c>
     </row>
     <row r="761">
@@ -50629,7 +50629,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>617807-5571-CM26</t>
+          <t>617807-5570-CM26</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -50688,13 +50688,13 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>49070.21</v>
+        <v>17119.75</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>3544-246-CM26</t>
+          <t>617807-5571-CM26</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -50714,17 +50714,17 @@
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>61.101.062-1</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
@@ -50753,13 +50753,13 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>1016.17</v>
+        <v>49070.21</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>617807-5570-CM26</t>
+          <t>3544-246-CM26</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -50779,17 +50779,17 @@
       </c>
       <c r="E775" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.101.062-1</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -50818,13 +50818,13 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>17119.75</v>
+        <v>1016.17</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>1079516-1101-CM26</t>
+          <t>1079516-1099-CM26</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -50883,13 +50883,13 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>14953.82</v>
+        <v>38257.59</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>1079516-1099-CM26</t>
+          <t>1079516-1101-CM26</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -50948,7 +50948,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>38257.59</v>
+        <v>14953.82</v>
       </c>
     </row>
     <row r="778">
@@ -51019,7 +51019,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>3047-618-CM26</t>
+          <t>1172239-126-CM26</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -51034,7 +51034,7 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -51044,12 +51044,12 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>61.930.100-5</t>
+          <t>62.000.820-6</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE VALPARAISO</t>
         </is>
       </c>
       <c r="H779" t="inlineStr">
@@ -51078,13 +51078,13 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>510.75</v>
+        <v>2291.57</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>3515-479-CM26</t>
+          <t>1172239-124-CM26</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -51099,7 +51099,7 @@
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E780" t="inlineStr">
@@ -51109,12 +51109,12 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>62.000.820-6</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE VALPARAISO</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
@@ -51143,13 +51143,13 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>6961.36</v>
+        <v>2291.57</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>1099834-111-CM26</t>
+          <t>3047-618-CM26</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -51164,7 +51164,7 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
@@ -51174,12 +51174,12 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>62.000.640-8</t>
+          <t>61.930.100-5</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
@@ -51208,72 +51208,397 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>3040.81</v>
+        <v>510.75</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
+          <t>4301-712-CM26</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>69.050.400-6</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M782" s="2" t="n">
+        <v>27589.53</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>3515-479-CM26</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>69.060.300-4</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M783" s="2" t="n">
+        <v>6961.36</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>1705-699-CM26</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>61.606.603-k</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>HOSPITAL ADRIANA COUSINO DE QUINTERO</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M784" s="2" t="n">
+        <v>23312.86</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>1099834-111-CM26</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>62.000.640-8</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA SAN FELIPE</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M785" s="2" t="n">
+        <v>3040.81</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
           <t>3544-254-CM26</t>
         </is>
       </c>
-      <c r="B782" t="inlineStr">
+      <c r="B786" t="inlineStr">
         <is>
           <t>2239-1-LR26</t>
         </is>
       </c>
-      <c r="C782" t="inlineStr">
+      <c r="C786" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D782" t="inlineStr">
+      <c r="D786" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E782" t="inlineStr">
+      <c r="E786" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F782" t="inlineStr">
+      <c r="F786" t="inlineStr">
         <is>
           <t>61.101.062-1</t>
         </is>
       </c>
-      <c r="G782" t="inlineStr">
+      <c r="G786" t="inlineStr">
         <is>
           <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
-      <c r="H782" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="I782" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J782" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K782" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L782" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M782" s="2" t="n">
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M786" s="2" t="n">
         <v>2027.2</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>1099402-559-CM26</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>62.000.620-3</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>CENTRO DE SALUD FAMILIAR CESFAM LLAY LLAY</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M787" s="2" t="n">
+        <v>13853.69</v>
       </c>
     </row>
   </sheetData>
